--- a/artfynd/A 9553-2025 artfynd.xlsx
+++ b/artfynd/A 9553-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>65906025</v>
       </c>
       <c r="B2" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>658985.6116731327</v>
+        <v>658986</v>
       </c>
       <c r="R2" t="n">
-        <v>6622892.782461512</v>
+        <v>6622893</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1997-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1997-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 9553-2025 artfynd.xlsx
+++ b/artfynd/A 9553-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65906025</v>
       </c>
       <c r="B2" t="n">
-        <v>99069</v>
+        <v>99070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9553-2025 artfynd.xlsx
+++ b/artfynd/A 9553-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65906025</v>
       </c>
       <c r="B2" t="n">
-        <v>99070</v>
+        <v>99071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9553-2025 artfynd.xlsx
+++ b/artfynd/A 9553-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65906025</v>
       </c>
       <c r="B2" t="n">
-        <v>99071</v>
+        <v>99074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9553-2025 artfynd.xlsx
+++ b/artfynd/A 9553-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65906025</v>
       </c>
       <c r="B2" t="n">
-        <v>99074</v>
+        <v>99073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9553-2025 artfynd.xlsx
+++ b/artfynd/A 9553-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65906025</v>
       </c>
       <c r="B2" t="n">
-        <v>99073</v>
+        <v>99079</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9553-2025 artfynd.xlsx
+++ b/artfynd/A 9553-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65906025</v>
       </c>
       <c r="B2" t="n">
-        <v>99079</v>
+        <v>99082</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9553-2025 artfynd.xlsx
+++ b/artfynd/A 9553-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65906025</v>
       </c>
       <c r="B2" t="n">
-        <v>99082</v>
+        <v>99087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9553-2025 artfynd.xlsx
+++ b/artfynd/A 9553-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>65906025</v>
+        <v>98362105</v>
       </c>
       <c r="B2" t="n">
-        <v>99089</v>
+        <v>92205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>O om Säbysjön, Upl</t>
+          <t>Noors Slott, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>658986</v>
+        <v>659029</v>
       </c>
       <c r="R2" t="n">
-        <v>6622893</v>
+        <v>6622756</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
+          <t>2021-11-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1997-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>2021-11-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,24 +760,478 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Granskog och äppelodling</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>98362104</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Noors Slott, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>659134</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6622797</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-11-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-11-25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>65715354</v>
+      </c>
+      <c r="B4" t="n">
+        <v>83314</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6471</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gulvit blekspik</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sclerophora pallida</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Noor slotts gamla fruktträdgård, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>658934</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6622752</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-05-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-05-21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Gammal fruktträdgård</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>päron</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pyrus communis</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Två gamla grova träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pyrus communis # Två gamla grova träd</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>65715735</v>
+      </c>
+      <c r="B5" t="n">
+        <v>83314</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6471</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulvit blekspik</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sclerophora pallida</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Noor slott, 400 m SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>658889</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6622874</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-05-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-05-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gles ädellövskog/hagmark</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Karin Martinsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>65906025</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99230</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>O om Säbysjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>658986</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6622893</v>
+      </c>
+      <c r="S6" t="n">
+        <v>100</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1997-01-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1997-12-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Granskog och äppelodling</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Mora Aronsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Mats Hannerz</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Upplands Flora 2010</t>
         </is>

--- a/artfynd/A 9553-2025 artfynd.xlsx
+++ b/artfynd/A 9553-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98362105</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
           <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98362104</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65715354</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65715735</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,8 +1261,20 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65906025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>